--- a/data/trans_dic/P3A$otraSIcobra-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraSIcobra-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y cobra por ello, se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y cobra por ello se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 6,67</t>
+          <t>3,5; 6,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,5; 8,31</t>
+          <t>5,37; 7,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,99; 7,08</t>
+          <t>4,99; 7,09</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,15</t>
+          <t>0,87; 2,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 1,89</t>
+          <t>0,97; 1,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,87</t>
+          <t>1,0; 1,8</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,24; 7,95</t>
+          <t>4,28; 7,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 7,88</t>
+          <t>4,75; 7,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,93; 7,21</t>
+          <t>4,94; 7,18</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,45</t>
+          <t>2,1; 3,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,74; 3,95</t>
+          <t>2,73; 3,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 3,48</t>
+          <t>2,61; 3,51</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y cobra por ello, se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y cobra por ello se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18769; 34362</t>
+          <t>18029; 33861</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41548; 62746</t>
+          <t>40558; 60248</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63454; 89984</t>
+          <t>63428; 90037</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20050; 49119</t>
+          <t>19870; 49698</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21819; 42325</t>
+          <t>21786; 42991</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46913; 84548</t>
+          <t>45274; 81569</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27413; 51376</t>
+          <t>27655; 50269</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32187; 52029</t>
+          <t>31374; 51515</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64396; 94230</t>
+          <t>64603; 93841</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>73624; 119017</t>
+          <t>72545; 119048</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>100259; 144146</t>
+          <t>99700; 142070</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>183179; 247055</t>
+          <t>185505; 249387</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$otraSIcobra-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraSIcobra-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 6,58</t>
+          <t>3,41; 6,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,37; 7,97</t>
+          <t>5,41; 8,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,99; 7,09</t>
+          <t>4,84; 6,9</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,17</t>
+          <t>1,06; 2,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,92</t>
+          <t>1,24; 2,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,8</t>
+          <t>1,28; 2,05</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,77</t>
+          <t>4,09; 7,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 7,8</t>
+          <t>4,91; 7,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,94; 7,18</t>
+          <t>4,87; 7,17</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,45</t>
+          <t>2,39; 3,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 3,89</t>
+          <t>3,2; 4,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 3,51</t>
+          <t>2,97; 3,73</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25224</t>
+          <t>27185</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50483</t>
+          <t>54869</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75707</t>
+          <t>82054</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18029; 33861</t>
+          <t>19753; 37118</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40558; 60248</t>
+          <t>44432; 66202</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63428; 90037</t>
+          <t>67733; 96628</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>32241</t>
+          <t>36047</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>30806</t>
+          <t>35723</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63047</t>
+          <t>71770</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19870; 49698</t>
+          <t>23527; 54129</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21786; 42991</t>
+          <t>26970; 46273</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45274; 81569</t>
+          <t>56171; 90058</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37586</t>
+          <t>39836</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41207</t>
+          <t>45862</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78792</t>
+          <t>85699</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>27655; 50269</t>
+          <t>29109; 52518</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31374; 51515</t>
+          <t>36054; 57776</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64603; 93841</t>
+          <t>70391; 103694</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>95050</t>
+          <t>103069</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>122496</t>
+          <t>136454</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>217547</t>
+          <t>239523</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>72545; 119048</t>
+          <t>84100; 126313</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>99700; 142070</t>
+          <t>119342; 156596</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>185505; 249387</t>
+          <t>215051; 270596</t>
         </is>
       </c>
     </row>
